--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486816_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486816_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6924</v>
+        <v>7.8136</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0314</v>
+        <v>6.5003</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6609</v>
+        <v>1.3133</v>
       </c>
       <c r="G2" t="n">
         <v>6.0527</v>
@@ -610,13 +610,13 @@
         <v>1.7377</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.831</v>
+        <v>-1.7098</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0486</v>
+        <v>-0.5797</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7824</v>
+        <v>-1.13</v>
       </c>
       <c r="V2" t="n">
         <v>2.6984</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. HERRERO ALONSO</t>
+          <t>A. ROSALES DARIAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3971</v>
+        <v>4.0481</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2193</v>
+        <v>2.555</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1778</v>
+        <v>1.4931</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9415</v>
+        <v>3.9681</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9722</v>
+        <v>0.6132</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.0307</v>
+        <v>3.3549</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7089</v>
+        <v>3.0034</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3183</v>
+        <v>0.4759</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.6094</v>
+        <v>2.5275</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2326</v>
+        <v>0.9646</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3461</v>
+        <v>0.1373</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5786</v>
+        <v>0.8274</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3862</v>
+        <v>1.5446</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.51</v>
+        <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5404</v>
+        <v>-1.179</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1097</v>
+        <v>-0.4484</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6501</v>
+        <v>-0.7306</v>
       </c>
       <c r="V3" t="n">
-        <v>4.3822</v>
+        <v>-0.2856</v>
       </c>
       <c r="W3" t="n">
-        <v>4.2969</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0852</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ROSALES DARIAS</t>
+          <t>J. HERRERO ALONSO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6108</v>
+        <v>3.6897</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3412</v>
+        <v>1.6609</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2696</v>
+        <v>2.0288</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9681</v>
+        <v>0.9415</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6132</v>
+        <v>1.9722</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3549</v>
+        <v>-1.0307</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0034</v>
+        <v>0.7089</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4759</v>
+        <v>2.3183</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5275</v>
+        <v>-1.6094</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9646</v>
+        <v>0.2326</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1373</v>
+        <v>-0.3461</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8274</v>
+        <v>0.5786</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5446</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5446</v>
+        <v>2.51</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.6162</v>
+        <v>-1.2478</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6622</v>
+        <v>-0.4488</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9540999999999999</v>
+        <v>-0.7991</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2856</v>
+        <v>4.3822</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.2969</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2856</v>
+        <v>0.0852</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8801</v>
+        <v>1.7974</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0946</v>
+        <v>0.2602</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7855</v>
+        <v>1.5372</v>
       </c>
       <c r="G5" t="n">
         <v>2.3488</v>
@@ -844,13 +844,13 @@
         <v>1.7377</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2409</v>
+        <v>-1.3237</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8002</v>
+        <v>-0.6347</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4407</v>
+        <v>-0.6891</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6136</v>
+        <v>1.0605</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9228</v>
+        <v>-1.5505</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5365</v>
+        <v>2.611</v>
       </c>
       <c r="G6" t="n">
         <v>0.2892</v>
@@ -922,13 +922,13 @@
         <v>2.51</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8533</v>
+        <v>-1.4065</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2141</v>
+        <v>-0.8417</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6392</v>
+        <v>-0.5647</v>
       </c>
       <c r="V6" t="n">
         <v>1.5985</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1646</v>
+        <v>0.268</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2283</v>
+        <v>-0.1249</v>
       </c>
       <c r="F7" t="n">
         <v>0.3929</v>
@@ -1000,10 +1000,10 @@
         <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1931</v>
+        <v>-0.0897</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3311</v>
+        <v>-0.2277</v>
       </c>
       <c r="U7" t="n">
         <v>0.138</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. ESTEBAN GLADER</t>
+          <t>M. SOSA FRANCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4589</v>
+        <v>-0.4503</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7729</v>
+        <v>-1.0771</v>
       </c>
       <c r="F8" t="n">
-        <v>0.314</v>
+        <v>0.6268</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4698</v>
+        <v>-0.7401</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6484</v>
+        <v>1.3374</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1786</v>
+        <v>-2.0775</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2969</v>
+        <v>-0.608</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6481</v>
+        <v>2.0278</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6488</v>
+        <v>-2.6358</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8270999999999999</v>
+        <v>-0.1321</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0003</v>
+        <v>-0.6904</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8274</v>
+        <v>0.5583</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0608</v>
+        <v>-1.0618</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5239</v>
+        <v>-0.4691</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4631</v>
+        <v>-0.5927</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.243</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SOSA FRANCO</t>
+          <t>I. ESTEBAN GLADER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8393</v>
+        <v>-0.9471000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2427</v>
+        <v>-1.1866</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4033</v>
+        <v>0.2395</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7401</v>
+        <v>-0.4698</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3374</v>
+        <v>-0.6484</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0775</v>
+        <v>0.1786</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.608</v>
+        <v>-1.2969</v>
       </c>
       <c r="K9" t="n">
-        <v>2.0278</v>
+        <v>-0.6481</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.6358</v>
+        <v>-0.6488</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1321</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6904</v>
+        <v>-0.0003</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5583</v>
+        <v>0.8274</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4508</v>
+        <v>-0.4274</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6347</v>
+        <v>0.1102</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8162</v>
+        <v>-0.5376</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.243</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1468</v>
+        <v>-1.0516</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8442</v>
+        <v>-0.9476</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3027</v>
+        <v>-0.104</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6503</v>
@@ -1234,13 +1234,13 @@
         <v>0.5792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4193</v>
+        <v>-0.324</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2756</v>
+        <v>0.1721</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6948</v>
+        <v>-0.4962</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6565</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5943</v>
+        <v>-2.0813</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7299</v>
+        <v>-2.3162</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1356</v>
+        <v>0.2349</v>
       </c>
       <c r="G11" t="n">
         <v>2.321</v>
@@ -1312,13 +1312,13 @@
         <v>0.9654</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1197</v>
+        <v>-0.6066</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6347</v>
+        <v>-0.221</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.485</v>
+        <v>-0.3857</v>
       </c>
       <c r="V11" t="n">
         <v>-0.8995</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.3193</v>
+        <v>14.147</v>
       </c>
       <c r="E12" t="n">
-        <v>2.9457</v>
+        <v>3.773500000000003</v>
       </c>
       <c r="F12" t="n">
-        <v>10.3734</v>
+        <v>10.3735</v>
       </c>
       <c r="G12" t="n">
         <v>14.0326</v>
@@ -1390,13 +1390,13 @@
         <v>13.5154</v>
       </c>
       <c r="S12" t="n">
-        <v>-10.2039</v>
+        <v>-9.376300000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.416399999999999</v>
+        <v>-3.5888</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.7876</v>
+        <v>-5.787699999999999</v>
       </c>
       <c r="V12" t="n">
         <v>6.594500000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. GONZALEZ GRANDE</t>
+          <t>P. RODRIGUEZ FAJARDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1851</v>
+        <v>1.9008</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3166</v>
+        <v>1.1086</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1315</v>
+        <v>0.7922</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.8273</v>
+        <v>0.5566</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.565</v>
+        <v>-0.4969</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2623</v>
+        <v>1.0535</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0131</v>
+        <v>0.3437</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.0131</v>
+        <v>0.538</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0.1943</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8142</v>
+        <v>0.2129</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-1.0349</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2623</v>
+        <v>1.2478</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4677</v>
+        <v>1.4134</v>
       </c>
       <c r="T13" t="n">
-        <v>4.3297</v>
+        <v>0.7649</v>
       </c>
       <c r="U13" t="n">
-        <v>0.138</v>
+        <v>0.6485</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2277</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3862</v>
+        <v>0.6758</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0619</v>
+        <v>0.3518</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4481</v>
+        <v>0.324</v>
       </c>
       <c r="G14" t="n">
         <v>-0.345</v>
@@ -1546,13 +1546,13 @@
         <v>0.3862</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0828</v>
+        <v>0.3723</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3863</v>
+        <v>0.0274</v>
       </c>
       <c r="U14" t="n">
-        <v>0.469</v>
+        <v>0.3449</v>
       </c>
       <c r="V14" t="n">
         <v>1.2277</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. PARRONDO CASTRO</t>
+          <t>P. GRIMA LORENZO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0142</v>
+        <v>0.145</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1041</v>
+        <v>1.8447</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09</v>
+        <v>-1.6997</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.9113</v>
+        <v>1.2394</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.2466</v>
+        <v>-0.4131</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6647</v>
+        <v>1.6525</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.1584</v>
+        <v>2.8616</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.591</v>
+        <v>2.2082</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5674</v>
+        <v>0.6534</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.753</v>
+        <v>-1.6222</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6557</v>
+        <v>-2.6213</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0973</v>
+        <v>0.9991</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.7377</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1585</v>
+        <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>4.4072</v>
+        <v>2.0753</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7227</v>
+        <v>0.9992</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6845</v>
+        <v>1.0762</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2277</v>
+        <v>-2.7836</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2277</v>
+        <v>-0.0852</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.6984</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ FAJARDO</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.158</v>
+        <v>-0.5137</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6496</v>
+        <v>-1.2434</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4916</v>
+        <v>0.7297</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5566</v>
+        <v>-1.3299</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4969</v>
+        <v>-0.1521</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0535</v>
+        <v>-1.1778</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3437</v>
+        <v>0.0784</v>
       </c>
       <c r="K16" t="n">
-        <v>0.538</v>
+        <v>1.5726</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1943</v>
+        <v>-1.4942</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2129</v>
+        <v>-1.4083</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0349</v>
+        <v>-1.7247</v>
       </c>
       <c r="O16" t="n">
-        <v>1.2478</v>
+        <v>0.3164</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1585</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1585</v>
+        <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6454</v>
+        <v>1.7237</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9933</v>
+        <v>0.9371</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3479</v>
+        <v>0.7865</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2277</v>
+        <v>-0.3282</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. GRIMA LORENZO</t>
+          <t>R. GONZALEZ GRANDE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3529</v>
+        <v>-0.7108</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5344</v>
+        <v>0.4208</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8873</v>
+        <v>-1.1315</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2394</v>
+        <v>-1.8273</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4131</v>
+        <v>-1.565</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6525</v>
+        <v>-0.2623</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8616</v>
+        <v>-1.0131</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2082</v>
+        <v>-1.0131</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6534</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6222</v>
+        <v>-0.8142</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.6213</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9991</v>
+        <v>-0.2623</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5446</v>
+        <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5775</v>
+        <v>1.5719</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6889</v>
+        <v>1.4339</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.138</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.7836</v>
+        <v>-1.2277</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.0852</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.6984</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.8524</v>
       </c>
       <c r="E18" t="n">
         <v>-0.6176</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1107</v>
+        <v>-0.2349</v>
       </c>
       <c r="G18" t="n">
         <v>0.6232</v>
@@ -1858,13 +1858,13 @@
         <v>0.5792</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0001</v>
+        <v>-0.1241</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3311</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3312</v>
+        <v>0.207</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>D. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.741</v>
+        <v>-1.7323</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0708</v>
+        <v>-0.9801</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3298</v>
+        <v>-0.7522</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3299</v>
+        <v>-1.3873</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1521</v>
+        <v>-1.3444</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1778</v>
+        <v>-0.043</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0784</v>
+        <v>-0.6421</v>
       </c>
       <c r="K19" t="n">
-        <v>1.5726</v>
+        <v>-0.7234</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4942</v>
+        <v>0.0814</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4083</v>
+        <v>-0.7453</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7247</v>
+        <v>-0.6209</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3164</v>
+        <v>-0.1244</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4963</v>
+        <v>-0.5034</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1098</v>
+        <v>-0.338</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3866</v>
+        <v>-0.1654</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3282</v>
+        <v>-0.6138</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. FLORES LUCAS</t>
+          <t>J. PARRONDO CASTRO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1226</v>
+        <v>-1.8565</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0835</v>
+        <v>-2.1726</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0391</v>
+        <v>0.3161</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.3873</v>
+        <v>-3.9113</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3444</v>
+        <v>-3.2466</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.043</v>
+        <v>-0.6647</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6421</v>
+        <v>-2.1584</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7234</v>
+        <v>-1.591</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0814</v>
+        <v>-0.5674</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7453</v>
+        <v>-1.753</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6209</v>
+        <v>-1.6557</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1244</v>
+        <v>-0.0973</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7723</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.8962</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8937</v>
+        <v>2.5649</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4415</v>
+        <v>1.6543</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4523</v>
+        <v>0.9106</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6138</v>
+        <v>1.2277</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>A. BRASSEUR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3878</v>
+        <v>-1.8763</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7624</v>
+        <v>-0.5722</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6254</v>
+        <v>-1.3041</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8073</v>
+        <v>-1.6139</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1381</v>
+        <v>0.9654</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6692</v>
+        <v>-2.5793</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.586</v>
+        <v>-0.5306</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1035</v>
+        <v>1.6554</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6895</v>
+        <v>-2.1859</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2212</v>
+        <v>-1.0833</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2415</v>
+        <v>-0.6899</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0203</v>
+        <v>-0.3934</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2869</v>
+        <v>0.193</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4966</v>
+        <v>-0.0417</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2097</v>
+        <v>0.2346</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2856</v>
+        <v>-1.2277</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. BRASSEUR</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.472</v>
+        <v>-2.032</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1927</v>
+        <v>-1.5556</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.2792</v>
+        <v>-0.4764</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6139</v>
+        <v>-1.8073</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9654</v>
+        <v>-1.1381</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5793</v>
+        <v>-0.6692</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5306</v>
+        <v>-0.586</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6554</v>
+        <v>0.1035</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.1859</v>
+        <v>-0.6895</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0833</v>
+        <v>-1.2212</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6899</v>
+        <v>-1.2415</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3934</v>
+        <v>0.0203</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7723</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7723</v>
+        <v>0.3862</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4027</v>
+        <v>0.0689</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6622</v>
+        <v>-0.2898</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2595</v>
+        <v>0.3587</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4896</v>
+        <v>-2.1793</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.2214</v>
+        <v>-1.9112</v>
       </c>
       <c r="F23" t="n">
         <v>-0.2681</v>
@@ -2248,10 +2248,10 @@
         <v>0.7723</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2757</v>
+        <v>0.5859</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1377</v>
+        <v>0.4479</v>
       </c>
       <c r="U23" t="n">
         <v>0.138</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.4242</v>
+        <v>-2.9086</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.4603</v>
+        <v>-5.0466</v>
       </c>
       <c r="F24" t="n">
-        <v>2.0361</v>
+        <v>2.1381</v>
       </c>
       <c r="G24" t="n">
         <v>-1.3059</v>
@@ -2326,13 +2326,13 @@
         <v>0.9654</v>
       </c>
       <c r="S24" t="n">
-        <v>1.1254</v>
+        <v>1.6411</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1098</v>
+        <v>0.5235</v>
       </c>
       <c r="U24" t="n">
-        <v>1.0156</v>
+        <v>1.1176</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3129</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-13.3193</v>
+        <v>-11.9403</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.3733</v>
+        <v>-10.3734</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.9457</v>
+        <v>-1.5668</v>
       </c>
       <c r="G25" t="n">
         <v>-14.0324</v>
@@ -2377,7 +2377,7 @@
         <v>-1.967</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.574899999999999</v>
+        <v>-3.5749</v>
       </c>
       <c r="K25" t="n">
         <v>1.386900000000001</v>
@@ -2404,13 +2404,13 @@
         <v>10.6193</v>
       </c>
       <c r="S25" t="n">
-        <v>10.204</v>
+        <v>11.5829</v>
       </c>
       <c r="T25" t="n">
-        <v>5.787599999999999</v>
+        <v>5.787600000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>4.4163</v>
+        <v>5.795199999999999</v>
       </c>
       <c r="V25" t="n">
         <v>-6.5944</v>
